--- a/Result/checksun_b2/2025-12-05.xlsx
+++ b/Result/checksun_b2/2025-12-05.xlsx
@@ -1057,15 +1057,11 @@
           <t>17.84</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>17.85</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>17.67</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1487,15 +1483,11 @@
           <t>17.84</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>17.67</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1917,15 +1909,11 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>17.83</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -2347,15 +2335,11 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>17.82</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2777,15 +2761,11 @@
           <t>17.79</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -3207,15 +3187,11 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3637,15 +3613,11 @@
           <t>17.74</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -4067,15 +4039,11 @@
           <t>17.75</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4497,15 +4465,11 @@
           <t>17.73</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>17.77</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4927,15 +4891,11 @@
           <t>17.69</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5357,15 +5317,11 @@
           <t>17.72</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17.67</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5788,15 +5744,11 @@
           <t>11.93</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>11.93</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -6032,7 +5984,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>9912</t>
@@ -6215,15 +6171,11 @@
           <t>11.92</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11.93</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6459,7 +6411,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>9912</t>
@@ -6642,15 +6598,11 @@
           <t>11.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>11.93</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -7073,15 +7025,11 @@
           <t>11.85</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>11.92</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>11.93</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7504,15 +7452,11 @@
           <t>11.81</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>11.91</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11.93</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7935,15 +7879,11 @@
           <t>11.85</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>11.91</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>11.93</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8366,15 +8306,11 @@
           <t>11.87</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>11.91</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8797,15 +8733,11 @@
           <t>11.91</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>11.92</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -9228,15 +9160,11 @@
           <t>11.94</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9474,7 +9402,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9659,15 +9587,11 @@
           <t>11.97</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9905,7 +9829,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10090,15 +10014,11 @@
           <t>11.98</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10520,15 +10440,11 @@
           <t>79.88</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>80.15</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>79.87</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>79.87</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10950,15 +10866,11 @@
           <t>80.3</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>80.17</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>79.91</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>80.17</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>79.91</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11380,15 +11292,11 @@
           <t>80.52000000000001</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>80.12</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>79.96</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>80.12</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>79.95999999999999</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11810,15 +11718,11 @@
           <t>80.44</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>80.06</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>80</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12056,7 +11960,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12240,15 +12144,11 @@
           <t>80.03999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>80.04</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>80.04000000000001</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12484,7 +12384,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>6637</t>
@@ -12666,15 +12570,11 @@
           <t>79.62</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>79.92</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>80.1</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>80.09999999999999</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12910,7 +12810,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>6637</t>
@@ -13092,15 +12996,11 @@
           <t>78.9</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>79.8</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>80.1</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>80.09999999999999</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13522,15 +13422,11 @@
           <t>78.55999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>79.75</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>80.12</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>80.12</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13952,15 +13848,11 @@
           <t>78.34</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>79.72</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>80.16</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>79.72</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>80.16</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14382,15 +14274,11 @@
           <t>78.62</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>79.8</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>80.26</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>80.26000000000001</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14812,15 +14700,11 @@
           <t>79.4</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>79.93</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>80.36</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>80.36</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15247,15 +15131,11 @@
           <t>29.21</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>29.22</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>29.05</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15682,15 +15562,11 @@
           <t>29.14</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>29.05</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -16117,15 +15993,11 @@
           <t>29.13</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>29.06</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16552,15 +16424,11 @@
           <t>29.11</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>29.14</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>29.06</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16987,15 +16855,11 @@
           <t>29.17000000000001</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>29.12</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>29.07</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>29.07</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17422,15 +17286,11 @@
           <t>29.28</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>29.08</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>29.08</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17668,7 +17528,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -17857,15 +17717,11 @@
           <t>29.3</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>29.09</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>29.1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18103,7 +17959,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18292,15 +18148,11 @@
           <t>29.28</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>29.07</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>29.12</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>29.12</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18538,7 +18390,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18727,15 +18579,11 @@
           <t>29.2</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>29.14</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>29.14</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18973,7 +18821,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19162,15 +19010,11 @@
           <t>29.13</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>29.15</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19408,7 +19252,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19597,15 +19441,11 @@
           <t>29.03</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>29.16</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -20027,15 +19867,11 @@
           <t>36.87</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>37.13</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>37</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20457,15 +20293,11 @@
           <t>36.65</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>37.17</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>36.99</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>36.99</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20887,15 +20719,11 @@
           <t>36.29000000000001</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>37.21</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>36.97</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>36.97</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21317,15 +21145,11 @@
           <t>36.07</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>36.96</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>36.96</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21747,15 +21571,11 @@
           <t>36.0</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>37.42</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>36.96</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>36.96</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22177,15 +21997,11 @@
           <t>35.89</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>37.62</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>36.96</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>36.96</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22607,15 +22423,11 @@
           <t>35.74</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>37.87</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>36.96</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>36.96</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -23037,15 +22849,11 @@
           <t>35.69</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>38.09</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23467,15 +23275,11 @@
           <t>35.57000000000001</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>36.89</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>36.89</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23897,15 +23701,11 @@
           <t>35.61</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>36.88</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>36.88</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24327,15 +24127,11 @@
           <t>36.19</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>38.81</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>36.87</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>36.87</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24757,15 +24553,11 @@
           <t>22.32</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>22.3</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25187,15 +24979,11 @@
           <t>22.29</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>22.31</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25617,15 +25405,11 @@
           <t>22.11</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>22.29</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>22.29</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -26047,15 +25831,11 @@
           <t>21.92</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>22.32</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>22.26</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>22.26</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26477,15 +26257,11 @@
           <t>21.77</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>22.22</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>22.22</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26907,15 +26683,11 @@
           <t>21.7</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>22.32</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>22.19</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>22.19</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27337,15 +27109,11 @@
           <t>21.68</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>22.16</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>22.16</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27767,15 +27535,11 @@
           <t>21.88</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>22.13</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>22.13</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28197,15 +27961,11 @@
           <t>22.12</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>22.11</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>22.11</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28627,15 +28387,11 @@
           <t>22.33</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>22.54</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>22.09</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>22.09</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29057,15 +28813,11 @@
           <t>22.53</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>22.62</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>22.06</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>22.06</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29487,15 +29239,11 @@
           <t>21.78</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>22.02</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>21.87</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>21.87</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29917,15 +29665,11 @@
           <t>21.88</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>21.97</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>21.92</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30161,7 +29905,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>3284</t>
@@ -30343,15 +30091,11 @@
           <t>21.92</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>21.93</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>21.97</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>21.97</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30589,7 +30333,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -30773,15 +30517,11 @@
           <t>21.94</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>22.04</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>22.04</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31019,7 +30759,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31203,15 +30943,11 @@
           <t>21.9</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>21.81</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>22.12</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>22.12</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31447,7 +31183,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>3284</t>
@@ -31629,15 +31369,11 @@
           <t>21.74</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>22.2</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -31873,7 +31609,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>3284</t>
@@ -32055,15 +31795,11 @@
           <t>21.48</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>21.74</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>22.27</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>22.27</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32485,15 +32221,11 @@
           <t>21.32</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>21.72</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>22.36</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32915,15 +32647,11 @@
           <t>21.15</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>21.69</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>22.41</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>22.41</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33345,15 +33073,11 @@
           <t>21.25</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>21.69</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>22.46</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33775,15 +33499,11 @@
           <t>21.49</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>21.76</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>22.52</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34209,15 +33929,11 @@
           <t>56.64</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>57.04</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>55.56</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>55.56</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34643,15 +34359,11 @@
           <t>56.23999999999999</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>55.47</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>55.47</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35077,15 +34789,11 @@
           <t>56.06</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>57.82</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>55.42</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>55.42</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35511,15 +35219,11 @@
           <t>55.98</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>57.98</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>55.37</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>55.37</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35945,15 +35649,11 @@
           <t>56.06</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>58.25</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>55.34</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>55.34</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36379,15 +36079,11 @@
           <t>55.8</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>58.23</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>55.31</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>55.31</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36813,15 +36509,11 @@
           <t>55.26000000000001</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>58.11</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>55.26</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>55.26</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37247,15 +36939,11 @@
           <t>54.96</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>57.98</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>55.25</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>55.25</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37681,15 +37369,11 @@
           <t>54.3</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>57.89</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>55.26</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>55.26</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38115,15 +37799,11 @@
           <t>53.7</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>57.77</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>55.32</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>55.32</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38549,15 +38229,11 @@
           <t>53.84</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>57.72</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>55.47</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>55.47</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -38979,15 +38655,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39225,7 +38897,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39409,15 +39081,11 @@
           <t>15.12</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>15.1</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39655,7 +39323,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -39839,15 +39507,11 @@
           <t>15.03</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>15.11</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40085,7 +39749,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40269,15 +39933,11 @@
           <t>15.02</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>14.89</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>15.14</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>15.14</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40515,7 +40175,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -40699,15 +40359,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>14.83</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>15.17</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -40945,7 +40601,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41129,15 +40785,11 @@
           <t>14.97</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>14.79</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>15.21</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41375,7 +41027,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -41559,15 +41211,11 @@
           <t>14.86</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>14.74</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>15.21</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -41805,7 +41453,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -41989,15 +41637,11 @@
           <t>14.9</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>14.73</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>15.21</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42235,7 +41879,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42419,15 +42063,11 @@
           <t>14.9</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>14.72</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42665,7 +42305,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -42849,15 +42489,11 @@
           <t>15.13</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>14.74</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>15.26</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>15.26</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43095,7 +42731,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43279,15 +42915,11 @@
           <t>15.54</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>15.29</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43709,15 +43341,11 @@
           <t>120.8</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>121.52</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>120.44</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>121.52</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>120.44</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44139,15 +43767,11 @@
           <t>121.4</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>121.32</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>120.59</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>121.32</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>120.59</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44569,15 +44193,11 @@
           <t>121.5</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>121.28</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>120.77</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>120.77</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -44999,15 +44619,11 @@
           <t>121.7</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>121.12</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>120.93</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>121.12</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>120.93</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45245,7 +44861,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45429,15 +45045,11 @@
           <t>121.8</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>121.02</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>121.14</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>121.02</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>121.14</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -45675,7 +45287,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -45859,15 +45471,11 @@
           <t>121.7</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>120.7</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>121.36</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>121.36</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46105,7 +45713,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46289,15 +45897,11 @@
           <t>120.6</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>120.2</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>121.53</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>121.53</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46535,7 +46139,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -46719,15 +46323,11 @@
           <t>120.7</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>119.72</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>121.86</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>119.72</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>121.86</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -46965,7 +46565,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47149,15 +46749,11 @@
           <t>120.3</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>119.22</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>122.04</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>119.22</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>122.04</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47395,7 +46991,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -47579,15 +47175,11 @@
           <t>120.5</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>118.82</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>122.18</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>118.82</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>122.18</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -47825,7 +47417,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48009,15 +47601,11 @@
           <t>121.7</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>118.45</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>122.28</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>122.28</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48439,15 +48027,11 @@
           <t>20.92</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>20.97</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>20.53</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>20.53</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -48869,15 +48453,11 @@
           <t>20.48</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>20.91</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>20.47</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>20.47</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49299,15 +48879,11 @@
           <t>20.12</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>20.43</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49729,15 +49305,11 @@
           <t>19.98</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>20.93</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>20.4</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50159,15 +49731,11 @@
           <t>19.95</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>20.98</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>20.37</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50589,15 +50157,11 @@
           <t>19.79</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51019,15 +50583,11 @@
           <t>19.66</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>21.05</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>20.28</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>20.28</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51449,15 +51009,11 @@
           <t>19.73</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>20.23</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>20.23</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -51879,15 +51435,11 @@
           <t>19.85</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>21.12</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>20.18</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>20.18</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52309,15 +51861,11 @@
           <t>20.21</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52739,15 +52287,11 @@
           <t>20.79</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>21.28</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>20.1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53170,15 +52714,11 @@
           <t>38.45999999999999</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>38.69</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>38.69</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53601,15 +53141,11 @@
           <t>38.45</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>38.67</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>38.71</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>38.71</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54032,15 +53568,11 @@
           <t>38.42999999999999</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>38.66</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>38.73</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>38.73</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54463,15 +53995,11 @@
           <t>38.42</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>38.64</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>38.74</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>38.74</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -54894,15 +54422,11 @@
           <t>38.44</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>38.64</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>38.76</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>38.76</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55325,15 +54849,11 @@
           <t>38.51000000000001</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>38.66</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>38.78</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>38.78</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -55756,15 +55276,11 @@
           <t>38.47</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>38.64</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>38.78</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>38.78</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56187,15 +55703,11 @@
           <t>38.45</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>38.62</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>38.79</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>38.79</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56618,15 +56130,11 @@
           <t>38.45</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>38.61</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>38.79</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>38.79</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57049,15 +56557,11 @@
           <t>38.54</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>38.61</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>38.81</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>38.81</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57480,15 +56984,11 @@
           <t>38.56</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>38.82</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>38.82</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -57910,15 +57410,11 @@
           <t>38.19</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>38.13</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58340,15 +57836,11 @@
           <t>38.17</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>38.23</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>38.11</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -58770,15 +58262,11 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>38.26</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>38.1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59200,15 +58688,11 @@
           <t>38.04</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>38.27</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>38.11</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59630,15 +59114,11 @@
           <t>37.98</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>38.3</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>38.12</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>38.12</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -60060,15 +59540,11 @@
           <t>37.86</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>38.14</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>38.14</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60490,15 +59966,11 @@
           <t>37.77999999999999</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>38.14</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>38.14</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -60920,15 +60392,11 @@
           <t>37.81</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>38.4</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>38.13</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61350,15 +60818,11 @@
           <t>37.84</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>38.12</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>38.12</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -61780,15 +61244,11 @@
           <t>38.01000000000001</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>38.51</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>38.14</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>38.14</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62210,15 +61670,11 @@
           <t>38.19</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>38.58</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>38.17</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>38.17</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -62643,15 +62099,11 @@
           <t>26.76</t>
         </is>
       </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>26.98</t>
-        </is>
-      </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>26.43</t>
-        </is>
+      <c r="AM145" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>26.43</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -63076,15 +62528,11 @@
           <t>26.7</t>
         </is>
       </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>26.96</t>
-        </is>
-      </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>26.43</t>
-        </is>
+      <c r="AM146" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>26.43</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -63509,15 +62957,11 @@
           <t>26.76</t>
         </is>
       </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>26.92</t>
-        </is>
-      </c>
-      <c r="AN147" t="inlineStr">
-        <is>
-          <t>26.44</t>
-        </is>
+      <c r="AM147" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>26.44</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -63942,15 +63386,11 @@
           <t>26.71</t>
         </is>
       </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>26.86</t>
-        </is>
-      </c>
-      <c r="AN148" t="inlineStr">
-        <is>
-          <t>26.47</t>
-        </is>
+      <c r="AM148" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>26.47</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -64375,15 +63815,11 @@
           <t>26.65</t>
         </is>
       </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>26.82</t>
-        </is>
-      </c>
-      <c r="AN149" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
+      <c r="AM149" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>26.5</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -64808,15 +64244,11 @@
           <t>26.52</t>
         </is>
       </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="AN150" t="inlineStr">
-        <is>
-          <t>26.52</t>
-        </is>
+      <c r="AM150" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>26.52</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -65241,15 +64673,11 @@
           <t>26.45</t>
         </is>
       </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>26.72</t>
-        </is>
-      </c>
-      <c r="AN151" t="inlineStr">
-        <is>
-          <t>26.54</t>
-        </is>
+      <c r="AM151" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>26.54</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -65674,15 +65102,11 @@
           <t>26.48</t>
         </is>
       </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>26.62</t>
-        </is>
-      </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>26.55</t>
-        </is>
+      <c r="AM152" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>26.55</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -66107,15 +65531,11 @@
           <t>26.39</t>
         </is>
       </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>26.57</t>
-        </is>
-      </c>
-      <c r="AN153" t="inlineStr">
-        <is>
-          <t>26.57</t>
-        </is>
+      <c r="AM153" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>26.57</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -66540,15 +65960,11 @@
           <t>26.42</t>
         </is>
       </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>26.52</t>
-        </is>
-      </c>
-      <c r="AN154" t="inlineStr">
-        <is>
-          <t>26.6</t>
-        </is>
+      <c r="AM154" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>26.6</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -66786,7 +66202,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -66973,15 +66389,11 @@
           <t>26.74</t>
         </is>
       </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="AN155" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
+      <c r="AM155" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>26.67</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
